--- a/Config/Sound.xlsx
+++ b/Config/Sound.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0038A1AF-8EEE-4723-957B-8BE8A7A831E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925E8FF8-CFD6-4A30-A10C-49B50B3B05C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-2340" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="90" windowWidth="21850" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -173,6 +173,14 @@
   </si>
   <si>
     <t>FlySwordHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShortBoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -498,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.08203125" customWidth="1"/>
@@ -744,6 +752,32 @@
         <v>0</v>
       </c>
       <c r="I12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>2004</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13">
+        <v>12004</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>1</v>
       </c>
     </row>

--- a/Config/Sound.xlsx
+++ b/Config/Sound.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925E8FF8-CFD6-4A30-A10C-49B50B3B05C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF64505E-DDF5-4C26-AF92-B9D7E55401DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="90" windowWidth="21850" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
   <si>
     <t>#</t>
   </si>
@@ -181,6 +181,46 @@
   </si>
   <si>
     <t>ShortBoom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹命中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet_Hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切割声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗音乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameBattleBGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleWin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示界面出场音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfirmTipShow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -506,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.08203125" customWidth="1"/>
@@ -642,22 +682,40 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7">
+        <v>10004</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>1001</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <v>10002</v>
+        <v>10005</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -674,24 +732,24 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>2001</v>
+        <v>1001</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E10">
-        <v>12001</v>
+        <v>10002</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -705,22 +763,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>2002</v>
+        <v>1002</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E11">
-        <v>12002</v>
+        <v>10003</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -730,43 +788,22 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>2003</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12">
-        <v>12003</v>
-      </c>
-      <c r="F12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0.7</v>
+      <c r="A12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E13">
-        <v>12004</v>
+        <v>12001</v>
       </c>
       <c r="F13" t="s">
         <v>35</v>
@@ -778,6 +815,136 @@
         <v>0</v>
       </c>
       <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>2002</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14">
+        <v>12002</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>2003</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15">
+        <v>12003</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>2004</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>12004</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>2005</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17">
+        <v>12007</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>2006</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18">
+        <v>12006</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>1</v>
       </c>
     </row>
